--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R2" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,17 +751,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R3" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,13 +857,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R2" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,13 +756,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R3" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,17 +861,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,7 +889,7 @@
         <v>126008793</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>126008841</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126008888</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>126008818</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>126008626</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>126008710</v>
       </c>
       <c r="B9" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R2" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,17 +751,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R3" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,13 +857,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126008748</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126008940</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>126008793</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>126008841</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126008888</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>126008818</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>126008626</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>126008710</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R2" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,13 +756,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R3" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,17 +861,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R2" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,17 +751,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R3" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,13 +857,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R2" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,13 +756,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R3" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,17 +861,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,7 +889,7 @@
         <v>126008793</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>126008841</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126008888</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>126008818</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>126008626</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>126008710</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R2" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,17 +751,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R3" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,13 +857,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008748</v>
+        <v>126008940</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565705</v>
+        <v>565796</v>
       </c>
       <c r="R2" t="n">
-        <v>7128770</v>
+        <v>7128758</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,13 +756,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008940</v>
+        <v>126008748</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565796</v>
+        <v>565705</v>
       </c>
       <c r="R3" t="n">
-        <v>7128758</v>
+        <v>7128770</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,17 +861,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,7 +889,7 @@
         <v>126008793</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>126008841</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126008888</v>
       </c>
       <c r="B6" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>126008818</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>126008626</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>126008710</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126008940</v>
+        <v>126008793</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565796</v>
+        <v>565731</v>
       </c>
       <c r="R2" t="n">
-        <v>7128758</v>
+        <v>7128678</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,17 +751,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126008748</v>
+        <v>126008818</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565705</v>
+        <v>565727</v>
       </c>
       <c r="R3" t="n">
-        <v>7128770</v>
+        <v>7128743</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126008793</v>
+        <v>126008841</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565731</v>
+        <v>565750</v>
       </c>
       <c r="R4" t="n">
-        <v>7128678</v>
+        <v>7128771</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126008841</v>
+        <v>126008888</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565750</v>
+        <v>565758</v>
       </c>
       <c r="R5" t="n">
-        <v>7128771</v>
+        <v>7128735</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126008888</v>
+        <v>126008940</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,26 +1090,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1126,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565758</v>
+        <v>565796</v>
       </c>
       <c r="R6" t="n">
-        <v>7128735</v>
+        <v>7128758</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1164,13 +1160,17 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall färsk</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126008818</v>
+        <v>126008626</v>
       </c>
       <c r="B7" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,24 +1200,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1230,7 +1234,7 @@
         <v>565727</v>
       </c>
       <c r="R7" t="n">
-        <v>7128743</v>
+        <v>7128722</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126008626</v>
+        <v>126008710</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,11 +1322,7 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565727</v>
+        <v>565757</v>
       </c>
       <c r="R8" t="n">
-        <v>7128722</v>
+        <v>7128736</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126008710</v>
+        <v>126008748</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565757</v>
+        <v>565705</v>
       </c>
       <c r="R9" t="n">
-        <v>7128736</v>
+        <v>7128770</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 28909-2025 artfynd.xlsx
+++ b/artfynd/A 28909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008793</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008818</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008940</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008626</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,8 +1533,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126008748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>